--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c71443b647942c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85fd2326209041b3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85fd2326209041b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3bc1d6497d141b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3bc1d6497d141b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R71178d9a117a4f5b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R71178d9a117a4f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d293818a62c4572"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d293818a62c4572"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd08d4fc1af814837"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd08d4fc1af814837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3d1d607f9674b4b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3d1d607f9674b4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R995456f53a154717"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R995456f53a154717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a02b1739fba43fe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a02b1739fba43fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89bc41236b2546d2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89bc41236b2546d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc05b2cbfd6a4674"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc05b2cbfd6a4674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb220e3fd466e41ee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb220e3fd466e41ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8077041694a84a95"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8077041694a84a95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R006b54ff416d4812"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R006b54ff416d4812"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4821a2ee27e4ab5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Formulas/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4821a2ee27e4ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re44f86a884784fd7"/>
   </x:sheets>
 </x:workbook>
 </file>
